--- a/data/Variables_simular.xlsx
+++ b/data/Variables_simular.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andresalvarez/Documents/chec-local-uiti-vano-interpreter/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C740FADB-1BD5-0E4C-B6F8-D15D20648B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E3E21C-AE82-8B45-AAED-7984B2E439BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
   <si>
     <t>Variable</t>
   </si>
@@ -67,9 +67,6 @@
     <t>categorical</t>
   </si>
   <si>
-    <t>0 | 1/0 | 1/4 | 10 | 11 | 134.6 | 2 | 2/0 | 250 | 266.8 | 3/0 | 3/8 | 336.4 | 350 | 4 | 4/0 | 500 | 6 | 795 | OPGW</t>
-  </si>
-  <si>
     <t>Es el calibre del neutro. Igual que el conductor, se cambia con obra y el escenario se lee como la ganancia de subir de calibre.</t>
   </si>
   <si>
@@ -281,6 +278,12 @@
   </si>
   <si>
     <t>1CC | 1CFR | 2CC | 2CFR | 2CR | 2RL | 3CC | 3CFR | 3CR | 3RL</t>
+  </si>
+  <si>
+    <t>2|1/0|2/0|4/0|1/4|3/8</t>
+  </si>
+  <si>
+    <t>0.5|5|10|15|25|30|37.5|45|50|75|100|112.5|150|225|250|300</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -709,18 +712,18 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -735,24 +738,24 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -761,18 +764,21 @@
         <v>400</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -787,21 +793,21 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -810,18 +816,18 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -839,18 +845,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -865,24 +871,24 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -894,12 +900,12 @@
         <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -908,24 +914,24 @@
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -937,18 +943,18 @@
         <v>11</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -957,21 +963,21 @@
         <v>657.57575757575705</v>
       </c>
       <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
         <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -980,24 +986,24 @@
         <v>97423.3</v>
       </c>
       <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
         <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1006,24 +1012,24 @@
         <v>1977033</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1032,24 +1038,24 @@
         <v>23.70000076293945</v>
       </c>
       <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
         <v>47</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>1.080000042915344</v>
@@ -1058,24 +1064,24 @@
         <v>53.639995574951172</v>
       </c>
       <c r="F17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
         <v>50</v>
-      </c>
-      <c r="H17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18">
         <v>2.1384997367858891</v>
@@ -1084,24 +1090,24 @@
         <v>35.284999847412109</v>
       </c>
       <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" t="s">
         <v>53</v>
-      </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1110,24 +1116,24 @@
         <v>18.44802284240723</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1136,24 +1142,24 @@
         <v>120</v>
       </c>
       <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" t="s">
         <v>58</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>59</v>
-      </c>
-      <c r="I20" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21">
         <v>1950</v>
@@ -1162,24 +1168,24 @@
         <v>2026</v>
       </c>
       <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" t="s">
         <v>62</v>
-      </c>
-      <c r="H21" t="s">
-        <v>59</v>
-      </c>
-      <c r="I21" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22">
         <v>1950</v>
@@ -1188,24 +1194,24 @@
         <v>2026</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23">
         <v>0.4</v>
@@ -1217,15 +1223,15 @@
         <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1234,24 +1240,24 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" t="s">
         <v>69</v>
-      </c>
-      <c r="H24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1260,24 +1266,24 @@
         <v>401</v>
       </c>
       <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
         <v>72</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>73</v>
-      </c>
-      <c r="I25" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <v>-76.205241150000006</v>
@@ -1286,24 +1292,24 @@
         <v>-74.635653550000001</v>
       </c>
       <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s">
         <v>76</v>
-      </c>
-      <c r="H26" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>4.8026678240000296</v>
@@ -1312,13 +1318,13 @@
         <v>5.7693647379999797</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
